--- a/src/test/resources/TestDriver/TestGL2/Test.xlsx
+++ b/src/test/resources/TestDriver/TestGL2/Test.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alijaffar/workspace/fyntrac-data/src/test/resources/TestDriver/TestGL2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C998C46C-04ED-BF4B-80E2-9E575ECCB1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B27C09-ED4B-C945-86F4-74D83E25F848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test" sheetId="1" r:id="rId1"/>
-    <sheet name="O_SubledgerMapping" sheetId="5" r:id="rId2"/>
-    <sheet name="O_GL1" sheetId="2" r:id="rId3"/>
-    <sheet name="O_GL2" sheetId="3" r:id="rId4"/>
-    <sheet name="O_GL3" sheetId="4" r:id="rId5"/>
+    <sheet name="O_GL1" sheetId="2" r:id="rId2"/>
+    <sheet name="O_GL2" sheetId="3" r:id="rId3"/>
+    <sheet name="O_GL3" sheetId="4" r:id="rId4"/>
+    <sheet name="O_SLM" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,15 +66,6 @@
     <t>EXECUTION</t>
   </si>
   <si>
-    <t>TestGL/ReferenceData/RefData_SBO_EVENTS.xlsx</t>
-  </si>
-  <si>
-    <t>TestGL/ActivityData/ActivityData_JAN1.xlsx</t>
-  </si>
-  <si>
-    <t>TestGL/ActivityData/ActivityData_FEB3.xlsx</t>
-  </si>
-  <si>
     <t>{"instrumentId": "LOAN1"}</t>
   </si>
   <si>
@@ -238,6 +229,15 @@
   </si>
   <si>
     <t>CASH CLEARING 103R</t>
+  </si>
+  <si>
+    <t>TestGL2/ReferenceData/RefData_SBO_EVENTS.xlsx</t>
+  </si>
+  <si>
+    <t>TestGL2/ActivityData/ActivityData_JAN1.xlsx</t>
+  </si>
+  <si>
+    <t>TestGL2/ActivityData/ActivityData_FEB3.xlsx</t>
   </si>
 </sst>
 </file>
@@ -548,7 +548,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -559,7 +559,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -581,7 +581,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -606,518 +606,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A89D7F6-D523-C64C-90A7-B094A2B5F06A}">
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F250FCE-25A0-4E2C-8833-A52C8653E7D2}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1140,54 +628,54 @@
   <sheetData>
     <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="13" x14ac:dyDescent="0.15">
@@ -1195,25 +683,25 @@
         <v>20220131</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
         <v>5000</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I3" s="4">
         <v>1000</v>
@@ -1228,7 +716,7 @@
         <v>102</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N3" s="4">
         <v>202201</v>
@@ -1239,25 +727,25 @@
         <v>20220131</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4">
         <v>2000</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -1272,7 +760,7 @@
         <v>102</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N4" s="4">
         <v>202201</v>
@@ -1283,25 +771,25 @@
         <v>20220131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" s="4">
         <v>3000</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4">
         <v>100000</v>
@@ -1316,7 +804,7 @@
         <v>102</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N5" s="4">
         <v>202201</v>
@@ -1327,25 +815,25 @@
         <v>20220131</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4">
         <v>2000</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -1360,7 +848,7 @@
         <v>102</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N6" s="4">
         <v>202201</v>
@@ -1371,25 +859,25 @@
         <v>20220228</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5">
         <v>20000</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5">
         <v>1000</v>
@@ -1404,7 +892,7 @@
         <v>103</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N7" s="5">
         <v>202202</v>
@@ -1415,25 +903,25 @@
         <v>20220228</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5">
         <v>5000</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -1448,7 +936,7 @@
         <v>103</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N8" s="5">
         <v>202202</v>
@@ -1459,25 +947,25 @@
         <v>20220228</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" s="7">
         <v>18000</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I9" s="5">
         <v>100000</v>
@@ -1492,7 +980,7 @@
         <v>103</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N9" s="5">
         <v>202202</v>
@@ -1503,25 +991,25 @@
         <v>20220228</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E10" s="5">
         <v>3000</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -1536,7 +1024,7 @@
         <v>103</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N10" s="5">
         <v>202202</v>
@@ -1547,25 +1035,25 @@
         <v>20220228</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="8">
         <v>1</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E11" s="9">
         <v>18000</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
@@ -1580,7 +1068,7 @@
         <v>103</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N11" s="8">
         <v>202202</v>
@@ -1591,25 +1079,25 @@
         <v>20220228</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" s="8">
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" s="8">
         <v>17000</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I12" s="8">
         <v>75000</v>
@@ -1624,7 +1112,7 @@
         <v>103</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N12" s="8">
         <v>202202</v>
@@ -1635,25 +1123,25 @@
         <v>20220228</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E13" s="4">
         <v>20000</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I13" s="4">
         <v>210</v>
@@ -1668,7 +1156,7 @@
         <v>103</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N13" s="4">
         <v>202202</v>
@@ -1679,25 +1167,25 @@
         <v>20220228</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E14" s="4">
         <v>19000</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -1712,7 +1200,7 @@
         <v>103</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N14" s="4">
         <v>202202</v>
@@ -1735,7 +1223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E37FC6D-0077-4D62-8A07-4B36BD0B9382}">
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1758,54 +1246,54 @@
   <sheetData>
     <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="13" x14ac:dyDescent="0.15">
@@ -1813,25 +1301,25 @@
         <v>20220131</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
         <v>5000</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I3" s="4">
         <v>2000</v>
@@ -1846,7 +1334,7 @@
         <v>102</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N3" s="4">
         <v>202201</v>
@@ -1857,25 +1345,25 @@
         <v>20220131</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4">
         <v>2000</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -1890,7 +1378,7 @@
         <v>102</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N4" s="4">
         <v>202201</v>
@@ -1901,25 +1389,25 @@
         <v>20220131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" s="4">
         <v>3000</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4">
         <v>200000</v>
@@ -1934,7 +1422,7 @@
         <v>102</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N5" s="4">
         <v>202201</v>
@@ -1945,25 +1433,25 @@
         <v>20220131</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4">
         <v>2000</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -1978,7 +1466,7 @@
         <v>102</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N6" s="4">
         <v>202201</v>
@@ -1989,25 +1477,25 @@
         <v>20220228</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5">
         <v>20000</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5">
         <v>2000</v>
@@ -2022,7 +1510,7 @@
         <v>103</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N7" s="5">
         <v>202202</v>
@@ -2033,25 +1521,25 @@
         <v>20220228</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5">
         <v>5000</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -2066,7 +1554,7 @@
         <v>103</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N8" s="5">
         <v>202202</v>
@@ -2077,25 +1565,25 @@
         <v>20220228</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" s="7">
         <v>18000</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I9" s="5">
         <v>200000</v>
@@ -2110,7 +1598,7 @@
         <v>103</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N9" s="5">
         <v>202202</v>
@@ -2121,25 +1609,25 @@
         <v>20220228</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E10" s="5">
         <v>3000</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -2154,7 +1642,7 @@
         <v>103</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N10" s="5">
         <v>202202</v>
@@ -2165,25 +1653,25 @@
         <v>20220228</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" s="4">
         <v>20000</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4">
         <v>310</v>
@@ -2198,7 +1686,7 @@
         <v>103</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N11" s="4">
         <v>202202</v>
@@ -2209,25 +1697,25 @@
         <v>20220228</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4">
         <v>19000</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -2242,7 +1730,7 @@
         <v>103</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N12" s="4">
         <v>202202</v>
@@ -2258,7 +1746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DCA791-2956-4EBF-88DD-8DA0DEE202B6}">
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2281,54 +1769,54 @@
   <sheetData>
     <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="13" x14ac:dyDescent="0.15">
@@ -2336,25 +1824,25 @@
         <v>20220131</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
         <v>5000</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I3" s="4">
         <v>3000</v>
@@ -2369,7 +1857,7 @@
         <v>102</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N3" s="4">
         <v>202201</v>
@@ -2380,25 +1868,25 @@
         <v>20220131</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4">
         <v>2000</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -2413,7 +1901,7 @@
         <v>102</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N4" s="4">
         <v>202201</v>
@@ -2424,25 +1912,25 @@
         <v>20220131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" s="4">
         <v>3000</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4">
         <v>300000</v>
@@ -2457,7 +1945,7 @@
         <v>102</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N5" s="4">
         <v>202201</v>
@@ -2468,25 +1956,25 @@
         <v>20220131</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4">
         <v>2000</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -2501,7 +1989,7 @@
         <v>102</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N6" s="4">
         <v>202201</v>
@@ -2512,25 +2000,25 @@
         <v>20220228</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5">
         <v>20000</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5">
         <v>3000</v>
@@ -2545,7 +2033,7 @@
         <v>103</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N7" s="5">
         <v>202202</v>
@@ -2556,25 +2044,25 @@
         <v>20220228</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5">
         <v>5000</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -2589,7 +2077,7 @@
         <v>103</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N8" s="5">
         <v>202202</v>
@@ -2600,25 +2088,25 @@
         <v>20220228</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" s="7">
         <v>18000</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I9" s="5">
         <v>300000</v>
@@ -2633,7 +2121,7 @@
         <v>103</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N9" s="5">
         <v>202202</v>
@@ -2644,25 +2132,25 @@
         <v>20220228</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E10" s="5">
         <v>3000</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -2677,7 +2165,7 @@
         <v>103</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N10" s="5">
         <v>202202</v>
@@ -2688,25 +2176,25 @@
         <v>20220228</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" s="4">
         <v>20000</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4">
         <v>410</v>
@@ -2721,7 +2209,7 @@
         <v>103</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N11" s="4">
         <v>202202</v>
@@ -2732,25 +2220,25 @@
         <v>20220228</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4">
         <v>19000</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -2765,7 +2253,7 @@
         <v>103</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N12" s="4">
         <v>202202</v>
@@ -2779,4 +2267,516 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A89D7F6-D523-C64C-90A7-B094A2B5F06A}">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>